--- a/data/raw/pembangunan/ipm_2023.xlsx
+++ b/data/raw/pembangunan/ipm_2023.xlsx
@@ -1,41 +1,242 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT\DATA ANALYST\north-sumatra-socioeconomic-information-system\north-sumatra-socioeconomic-information-system\data\raw\pembangunan\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2842FFD-D10A-4EBE-896D-ACC34BA6E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="380" yWindow="380" windowWidth="13780" windowHeight="9130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+  <si>
+    <t>Kabupaten/Kota</t>
+  </si>
+  <si>
+    <t>Indeks Pembangunan Manusia</t>
+  </si>
+  <si>
+    <t>Nias</t>
+  </si>
+  <si>
+    <t>65.15</t>
+  </si>
+  <si>
+    <t>Mandailing Natal</t>
+  </si>
+  <si>
+    <t>72.65</t>
+  </si>
+  <si>
+    <t>Tapanuli Selatan</t>
+  </si>
+  <si>
+    <t>74.58</t>
+  </si>
+  <si>
+    <t>Tapanuli Tengah</t>
+  </si>
+  <si>
+    <t>72.77</t>
+  </si>
+  <si>
+    <t>Tapanuli Utara</t>
+  </si>
+  <si>
+    <t>76.86</t>
+  </si>
+  <si>
+    <t>Toba Samosir</t>
+  </si>
+  <si>
+    <t>77.83</t>
+  </si>
+  <si>
+    <t>Labuhan Batu</t>
+  </si>
+  <si>
+    <t>74.7</t>
+  </si>
+  <si>
+    <t>Asahan</t>
+  </si>
+  <si>
+    <t>73.59</t>
+  </si>
+  <si>
+    <t>Simalungun</t>
+  </si>
+  <si>
+    <t>75.17</t>
+  </si>
+  <si>
+    <t>Dairi</t>
+  </si>
+  <si>
+    <t>75.18</t>
+  </si>
+  <si>
+    <t>Karo</t>
+  </si>
+  <si>
+    <t>76.88</t>
+  </si>
+  <si>
+    <t>Deli Serdang</t>
+  </si>
+  <si>
+    <t>77.16</t>
+  </si>
+  <si>
+    <t>Langkat</t>
+  </si>
+  <si>
+    <t>74.33</t>
+  </si>
+  <si>
+    <t>Nias Selatan</t>
+  </si>
+  <si>
+    <t>64.98</t>
+  </si>
+  <si>
+    <t>Humbang Hasundutan</t>
+  </si>
+  <si>
+    <t>72.49</t>
+  </si>
+  <si>
+    <t>Pakpak Bharat</t>
+  </si>
+  <si>
+    <t>72.3</t>
+  </si>
+  <si>
+    <t>Samosir</t>
+  </si>
+  <si>
+    <t>72.93</t>
+  </si>
+  <si>
+    <t>Serdang Bedagai</t>
+  </si>
+  <si>
+    <t>73.4</t>
+  </si>
+  <si>
+    <t>Batu Bara</t>
+  </si>
+  <si>
+    <t>72.56</t>
+  </si>
+  <si>
+    <t>Padang Lawas Utara</t>
+  </si>
+  <si>
+    <t>73.45</t>
+  </si>
+  <si>
+    <t>Padang Lawas</t>
+  </si>
+  <si>
+    <t>72.16</t>
+  </si>
+  <si>
+    <t>Labuhan Batu Selatan</t>
+  </si>
+  <si>
+    <t>74.23</t>
+  </si>
+  <si>
+    <t>Labuhan Batu Utara</t>
+  </si>
+  <si>
+    <t>75.45</t>
+  </si>
+  <si>
+    <t>Nias Utara</t>
+  </si>
+  <si>
+    <t>65.44</t>
+  </si>
+  <si>
+    <t>Nias Barat</t>
+  </si>
+  <si>
+    <t>64.68</t>
+  </si>
+  <si>
+    <t>Kota Sibolga</t>
+  </si>
+  <si>
+    <t>77.07</t>
+  </si>
+  <si>
+    <t>Kota Tanjung Balai</t>
+  </si>
+  <si>
+    <t>75.42</t>
+  </si>
+  <si>
+    <t>Kota Pematang Siantar</t>
+  </si>
+  <si>
+    <t>80.46</t>
+  </si>
+  <si>
+    <t>Kota Tebing Tinggi</t>
+  </si>
+  <si>
+    <t>78.17</t>
+  </si>
+  <si>
+    <t>Kota Medan</t>
+  </si>
+  <si>
+    <t>82.61</t>
+  </si>
+  <si>
+    <t>Kota Binjai</t>
+  </si>
+  <si>
+    <t>78.11</t>
+  </si>
+  <si>
+    <t>Kota Padangsidimpuan</t>
+  </si>
+  <si>
+    <t>78.1</t>
+  </si>
+  <si>
+    <t>Kota Gunungsitoli</t>
+  </si>
+  <si>
+    <t>71.55</t>
+  </si>
+  <si>
+    <t>Sumatera Utara</t>
+  </si>
+  <si>
+    <t>75.13</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +266,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,302 +605,299 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Provinsi</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="str">
-        <v>Indeks Pembangunan Manusia (IPM) Provinsi Sumatera Utara Menurut Kabupaten/Kota (Persen)</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="str">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Sumatera Utara</v>
-      </c>
-      <c r="B4" t="str">
-        <v>67.09</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Nias</v>
-      </c>
-      <c r="B5" t="str">
-        <v>54.72</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Mandailing Natal</v>
-      </c>
-      <c r="B6" t="str">
-        <v>60.76</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Tapanuli Selatan</v>
-      </c>
-      <c r="B7" t="str">
-        <v>64.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Tapanuli Tengah</v>
-      </c>
-      <c r="B8" t="str">
-        <v>64.39</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Tapanuli Utara</v>
-      </c>
-      <c r="B9" t="str">
-        <v>68.43</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Toba</v>
-      </c>
-      <c r="B10" t="str">
-        <v>70.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Labuhan Batu</v>
-      </c>
-      <c r="B11" t="str">
-        <v>66.88</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Asahan</v>
-      </c>
-      <c r="B12" t="str">
-        <v>65.06</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Simalungun</v>
-      </c>
-      <c r="B13" t="str">
-        <v>68.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Dairi</v>
-      </c>
-      <c r="B14" t="str">
-        <v>65.91</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Karo</v>
-      </c>
-      <c r="B15" t="str">
-        <v>70.36</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Deli Serdang</v>
-      </c>
-      <c r="B16" t="str">
-        <v>70.06</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Langkat</v>
-      </c>
-      <c r="B17" t="str">
-        <v>64.57</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Nias Selatan</v>
-      </c>
-      <c r="B18" t="str">
-        <v>54.54</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Humbang Hasundutan</v>
-      </c>
-      <c r="B19" t="str">
-        <v>63.4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Pakpak Bharat</v>
-      </c>
-      <c r="B20" t="str">
-        <v>61.76</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Samosir</v>
-      </c>
-      <c r="B21" t="str">
-        <v>65.14</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Serdang Bedagai</v>
-      </c>
-      <c r="B22" t="str">
-        <v>64.67</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Batu Bara</v>
-      </c>
-      <c r="B23" t="str">
-        <v>63.45</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Padang Lawas Utara</v>
-      </c>
-      <c r="B24" t="str">
-        <v>64.25</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Padang Lawas</v>
-      </c>
-      <c r="B25" t="str">
-        <v>62.45</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Labuhanbatu Selatan</v>
-      </c>
-      <c r="B26" t="str">
-        <v>65.32</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Labuanbatu Utara</v>
-      </c>
-      <c r="B27" t="str">
-        <v>66.72</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Nias Utara</v>
-      </c>
-      <c r="B28" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Nias Barat</v>
-      </c>
-      <c r="B29" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Sibolga</v>
-      </c>
-      <c r="B30" t="str">
-        <v>68.37</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Tanjungbalai</v>
-      </c>
-      <c r="B31" t="str">
-        <v>63.47</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Pematangsiantar</v>
-      </c>
-      <c r="B32" t="str">
-        <v>72.52</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Tebing Tinggi</v>
-      </c>
-      <c r="B33" t="str">
-        <v>69.96</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Medan</v>
-      </c>
-      <c r="B34" t="str">
-        <v>77.02</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Binjai</v>
-      </c>
-      <c r="B35" t="str">
-        <v>70.54</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Padangsidimpuan</v>
-      </c>
-      <c r="B36" t="str">
-        <v>70.23</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>Gunungsitoli</v>
-      </c>
-      <c r="B37" t="str">
-        <v>-</v>
-      </c>
-    </row>
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="38" spans="1:2" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="1:2" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="41" spans="1:2" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="42" spans="1:2" ht="15.5" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:A3"/>
-  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B37"/>
+    <ignoredError sqref="A1:H36" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>